--- a/setting_lang/zh_lang_setting.xlsx
+++ b/setting_lang/zh_lang_setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24740" windowHeight="10860"/>
+    <workbookView windowWidth="24740" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="deepseek_csv_20250611_f42037" sheetId="1" r:id="rId1"/>
